--- a/news_push_data/all_news/cnyes/20260401 鉅亨網新聞.xlsx
+++ b/news_push_data/all_news/cnyes/20260401 鉅亨網新聞.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>等待確認的反攻訊號、太空計畫、記憶體、BBU、【鈦昇第二？】歡迎大家共襄盛舉 | 鉅亨網 - 專家觀點</t>
+          <t>三星SK海力士吃下定心丸！韓產業部拍胸脯：氦氣庫存撐到6月 上半年絕不斷鏈 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-03-31 17:25</t>
+          <t>2026-03-31 17:10</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-31T17:25:54+08:00</t>
+          <t>2026-03-31T17:10:05+08:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402897</t>
+          <t>https://news.cnyes.com/news/id/6402829</t>
         </is>
       </c>
     </row>
@@ -1126,22 +1126,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>三星SK海力士吃下定心丸！韓產業部拍胸脯：氦氣庫存撐到6月 上半年絕不斷鏈 | 鉅亨網 - 國際政經</t>
+          <t>Eutelsat擴大火箭供應來源，洽談印度ISRO發射合作以降低對SpaceX依賴 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-03-31 17:10</t>
+          <t>2026-03-31 17:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-31T17:10:05+08:00</t>
+          <t>2026-03-31T17:00:36+08:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402829</t>
+          <t>https://news.cnyes.com/news/id/6402849</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Eutelsat擴大火箭供應來源，洽談印度ISRO發射合作以降低對SpaceX依賴 | 鉅亨網 - 國際政經</t>
+          <t>中國證實已有3艘船成功穿越荷莫茲海峽，中遠海控正嘗試恢復接單訂艙 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402849</t>
+          <t>https://news.cnyes.com/news/id/6402848</t>
         </is>
       </c>
     </row>
@@ -1180,22 +1180,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中國證實已有3艘船成功穿越荷莫茲海峽，中遠海控正嘗試恢復接單訂艙 | 鉅亨網 - 國際政經</t>
+          <t>不是賺太少，而是花錯了！有錢人從不做的三種消費 | 鉅亨網 - 專家觀點</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00</t>
+          <t>2026-03-31 16:05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-31T17:00:36+08:00</t>
+          <t>2026-03-31T16:05:47+08:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402848</t>
+          <t>https://news.cnyes.com/news/id/6402721</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>台股重挫失守32000點！AI族群補跌壓力浮現，鎖定「五路財神」錯殺點位 | 鉅亨網 - 台股新聞</t>
+          <t>戰火燒向鋁市！中東兩大鋁廠受損 鋁價單月暴漲10%、創近兩年最大增幅 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-03-31 16:46</t>
+          <t>2026-03-31 15:57</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-31T16:46:04+08:00</t>
+          <t>2026-03-31T15:57:27+08:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402828</t>
+          <t>https://news.cnyes.com/news/id/6402287</t>
         </is>
       </c>
     </row>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>不是賺太少，而是花錯了！有錢人從不做的三種消費 | 鉅亨網 - 專家觀點</t>
+          <t>抨擊美國和平方案「過度且不合理」 伊朗：研議退出《不擴散核武條約》 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-03-31 16:05</t>
+          <t>2026-03-31 15:40</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-31T16:05:47+08:00</t>
+          <t>2026-03-31T15:40:11+08:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402721</t>
+          <t>https://news.cnyes.com/news/id/6402544</t>
         </is>
       </c>
     </row>
@@ -1261,22 +1261,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>戰火燒向鋁市！中東兩大鋁廠受損 鋁價單月暴漲10%、創近兩年最大增幅 | 鉅亨網 - 國際政經</t>
+          <t>憂伊朗戰爭衝擊經濟！亞洲信用風險三月恐創2023年以來單月最大飆升 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-03-31 15:57</t>
+          <t>2026-03-31 15:40</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-31T15:57:27+08:00</t>
+          <t>2026-03-31T15:40:07+08:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402287</t>
+          <t>https://news.cnyes.com/news/id/6402501</t>
         </is>
       </c>
     </row>
@@ -1288,22 +1288,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>抨擊美國和平方案「過度且不合理」 伊朗：研議退出《不擴散核武條約》 | 鉅亨網 - 國際政經</t>
+          <t>伊朗戰火未停 美軍重磅轟炸伊斯法罕 鑽地彈鎖定核心設施 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-03-31 15:40</t>
+          <t>2026-03-31 15:20</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-31T15:40:11+08:00</t>
+          <t>2026-03-31T15:20:04+08:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402544</t>
+          <t>https://news.cnyes.com/news/id/6402526</t>
         </is>
       </c>
     </row>
@@ -1315,22 +1315,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>憂伊朗戰爭衝擊經濟！亞洲信用風險三月恐創2023年以來單月最大飆升 | 鉅亨網 - 國際政經</t>
+          <t>黎巴嫩真主黨強化攻勢 成襲擊以色列北部主力 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-03-31 15:40</t>
+          <t>2026-03-31 14:50</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-31T15:40:07+08:00</t>
+          <t>2026-03-31T14:50:03+08:00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402501</t>
+          <t>https://news.cnyes.com/news/id/6402502</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>伊朗戰火未停 美軍重磅轟炸伊斯法罕 鑽地彈鎖定核心設施 | 鉅亨網 - 國際政經</t>
+          <t>防衛大臣：日本首次部署具備「對敵基地攻擊能力」長程飛彈 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-03-31 15:20</t>
+          <t>2026-03-31 14:19</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-31T15:20:04+08:00</t>
+          <t>2026-03-31T14:19:40+08:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402526</t>
+          <t>https://news.cnyes.com/news/id/6402536</t>
         </is>
       </c>
     </row>
@@ -1369,22 +1369,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>黎巴嫩真主黨強化攻勢 成襲擊以色列北部主力 | 鉅亨網 - 國際政經</t>
+          <t>納坦雅胡宣稱對伊戰爭任務已達成過半 未訂時間表 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-03-31 14:50</t>
+          <t>2026-03-31 13:58</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-31T14:50:03+08:00</t>
+          <t>2026-03-31T13:58:02+08:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402502</t>
+          <t>https://news.cnyes.com/news/id/6402531</t>
         </is>
       </c>
     </row>
@@ -1396,22 +1396,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>防衛大臣：日本首次部署具備「對敵基地攻擊能力」長程飛彈 | 鉅亨網 - 國際政經</t>
+          <t>荷姆茲海峽替代航線也陷入危險！傳伊朗促胡塞武裝備戰紅海航運 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-03-31 14:19</t>
+          <t>2026-03-31 13:49</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-31T14:19:40+08:00</t>
+          <t>2026-03-31T13:49:31+08:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402536</t>
+          <t>https://news.cnyes.com/news/id/6401968</t>
         </is>
       </c>
     </row>
@@ -1423,22 +1423,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>納坦雅胡宣稱對伊戰爭任務已達成過半 未訂時間表 | 鉅亨網 - 國際政經</t>
+          <t>南韓石腦油供應拉警報，LG化學麗水廠停工後再示警俄羅斯原料取得困難 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-03-31 13:58</t>
+          <t>2026-03-31 12:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-31T13:58:02+08:00</t>
+          <t>2026-03-31T12:00:32+08:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402531</t>
+          <t>https://news.cnyes.com/news/id/6402355</t>
         </is>
       </c>
     </row>
@@ -1450,22 +1450,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>荷姆茲海峽替代航線也陷入危險！傳伊朗促胡塞武裝備戰紅海航運 | 鉅亨網 - 國際政經</t>
+          <t>上月底以來首次！兩艘中國貨櫃船通過荷姆茲海峽 | 鉅亨網 - 大陸政經</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-03-31 13:49</t>
+          <t>2026-03-31 11:56</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-31T13:49:31+08:00</t>
+          <t>2026-03-31T11:56:25+08:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6401968</t>
+          <t>https://news.cnyes.com/news/id/6402298</t>
         </is>
       </c>
     </row>
@@ -1477,22 +1477,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>南韓石腦油供應拉警報，LG化學麗水廠停工後再示警俄羅斯原料取得困難 | 鉅亨網 - 國際政經</t>
+          <t>美伊和談露曙光？美國稱與伊朗「談判順利」、批伊朗公開與私下兩副面孔 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-03-31 12:00</t>
+          <t>2026-03-31 11:38</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-31T12:00:32+08:00</t>
+          <t>2026-03-31T11:38:10+08:00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402355</t>
+          <t>https://news.cnyes.com/news/id/6401965</t>
         </is>
       </c>
     </row>
@@ -1504,22 +1504,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>上月底以來首次！兩艘中國貨櫃船通過荷姆茲海峽 | 鉅亨網 - 大陸政經</t>
+          <t>日本電裝DENSO訂2030目標營收拚8兆日圓加碼車用半導體布局 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-03-31 11:56</t>
+          <t>2026-03-31 11:30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-31T11:56:25+08:00</t>
+          <t>2026-03-31T11:30:12+08:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402298</t>
+          <t>https://news.cnyes.com/news/id/6402271</t>
         </is>
       </c>
     </row>
@@ -1531,22 +1531,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>美伊和談露曙光？美國稱與伊朗「談判順利」、批伊朗公開與私下兩副面孔 | 鉅亨網 - 國際政經</t>
+          <t>美國駐委內瑞拉大使館 正式恢復運作 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-03-31 11:38</t>
+          <t>2026-03-31 11:26</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-31T11:38:10+08:00</t>
+          <t>2026-03-31T11:26:33+08:00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6401965</t>
+          <t>https://news.cnyes.com/news/id/6401967</t>
         </is>
       </c>
     </row>
@@ -1558,22 +1558,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>日本電裝DENSO訂2030目標營收拚8兆日圓加碼車用半導體布局 | 鉅亨網 - 國際政經</t>
+          <t>美以伊開戰第31天戰況彙整：荷姆茲海峽持續緊張、伊朗與美國發聲 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-03-31 11:30</t>
+          <t>2026-03-31 11:03</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-31T11:30:12+08:00</t>
+          <t>2026-03-31T11:03:09+08:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402271</t>
+          <t>https://news.cnyes.com/news/id/6402189</t>
         </is>
       </c>
     </row>
@@ -1585,22 +1585,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>美國駐委內瑞拉大使館 正式恢復運作 | 鉅亨網 - 國際政經</t>
+          <t>川普鬆口？不介意俄羅斯向古巴運送石油 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-03-31 11:26</t>
+          <t>2026-03-31 10:45</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-31T11:26:33+08:00</t>
+          <t>2026-03-31T10:45:02+08:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6401967</t>
+          <t>https://news.cnyes.com/news/id/6401955</t>
         </is>
       </c>
     </row>
@@ -1612,22 +1612,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>美以伊開戰第31天戰況彙整：荷姆茲海峽持續緊張、伊朗與美國發聲 | 鉅亨網 - 國際政經</t>
+          <t>中東戰火最大贏家？憑藉地理隔絕優勢 「這地方」正成為全球能源新避風港 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-03-31 11:03</t>
+          <t>2026-03-31 10:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-31T11:03:09+08:00</t>
+          <t>2026-03-31T10:00:05+08:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402189</t>
+          <t>https://news.cnyes.com/news/id/6401739</t>
         </is>
       </c>
     </row>
@@ -1639,22 +1639,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>川普鬆口？不介意俄羅斯向古巴運送石油 | 鉅亨網 - 國際政經</t>
+          <t>伊朗高層談格陵蘭島 稱丹麥可向伊朗尋求協助 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-03-31 10:45</t>
+          <t>2026-03-31 09:45</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-31T10:45:02+08:00</t>
+          <t>2026-03-31T09:45:51+08:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6401955</t>
+          <t>https://news.cnyes.com/news/id/6401956</t>
         </is>
       </c>
     </row>
@@ -1666,22 +1666,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>中東戰火最大贏家？憑藉地理隔絕優勢 「這地方」正成為全球能源新避風港 | 鉅亨網 - 國際政經</t>
+          <t>即使荷姆茲海峽仍封鎖 華爾街日報：川普也願結束戰爭 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-03-31 10:00</t>
+          <t>2026-03-31 09:21</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-31T10:00:05+08:00</t>
+          <t>2026-03-31T09:21:51+08:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6401739</t>
+          <t>https://news.cnyes.com/news/id/6402032</t>
         </is>
       </c>
     </row>
@@ -1693,22 +1693,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>伊朗高層談格陵蘭島 稱丹麥可向伊朗尋求協助 | 鉅亨網 - 國際政經</t>
+          <t>人道例外？古巴收3個月首批原油 白宮強調：制裁政策未改 只放行一次 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-03-31 09:45</t>
+          <t>2026-03-31 09:10</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-31T09:45:51+08:00</t>
+          <t>2026-03-31T09:10:05+08:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6401956</t>
+          <t>https://news.cnyes.com/news/id/6401928</t>
         </is>
       </c>
     </row>
@@ -1720,22 +1720,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>即使荷姆茲海峽仍封鎖 華爾街日報：川普也願結束戰爭 | 鉅亨網 - 國際政經</t>
+          <t>韓媒：美光科技嘗試垂直堆疊GDDR 欲在標準GDDR與HBM之間開闢新路 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-03-31 09:21</t>
+          <t>2026-03-31 09:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-31T09:21:51+08:00</t>
+          <t>2026-03-31T09:00:09+08:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6402032</t>
+          <t>https://news.cnyes.com/news/id/6401757</t>
         </is>
       </c>
     </row>
@@ -1747,22 +1747,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>人道例外？古巴收3個月首批原油 白宮強調：制裁政策未改 只放行一次 | 鉅亨網 - 國際政經</t>
+          <t>海軍司令被炸死！伊朗最高領袖、總統發唁電 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-03-31 09:10</t>
+          <t>2026-03-31 08:42</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-31T09:10:05+08:00</t>
+          <t>2026-03-31T08:42:40+08:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6401928</t>
+          <t>https://news.cnyes.com/news/id/6401958</t>
         </is>
       </c>
     </row>
@@ -1774,22 +1774,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>韓媒：美光科技嘗試垂直堆疊GDDR 欲在標準GDDR與HBM之間開闢新路 | 鉅亨網 - 國際政經</t>
+          <t>伊朗襲擊中東兩大鋁冶煉廠美國鋁供應鏈承壓LME鋁價飆升至4年高點附近 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-03-31 09:00</t>
+          <t>2026-03-31 08:30</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-31T09:00:09+08:00</t>
+          <t>2026-03-31T08:30:03+08:00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6401757</t>
+          <t>https://news.cnyes.com/news/id/6401991</t>
         </is>
       </c>
     </row>
@@ -1801,22 +1801,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>海軍司令被炸死！伊朗最高領袖、總統發唁電 | 鉅亨網 - 國際政經</t>
+          <t>伊朗國會初步批准荷姆茲海峽過路費法案 伊朗本幣付錢 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-03-31 08:42</t>
+          <t>2026-03-31 08:25</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-31T08:42:40+08:00</t>
+          <t>2026-03-31T08:25:34+08:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6401958</t>
+          <t>https://news.cnyes.com/news/id/6401957</t>
         </is>
       </c>
     </row>
@@ -1828,22 +1828,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>伊朗襲擊中東兩大鋁冶煉廠美國鋁供應鏈承壓LME鋁價飆升至4年高點附近 | 鉅亨網 - 國際政經</t>
+          <t>油價竄升 盟友盼別攻俄油設施 澤倫斯基：俄方停攻能源 烏願對等降級衝突 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-03-31 08:30</t>
+          <t>2026-03-31 08:10</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-31T08:30:03+08:00</t>
+          <t>2026-03-31T08:10:02+08:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6401991</t>
+          <t>https://news.cnyes.com/news/id/6401920</t>
         </is>
       </c>
     </row>
@@ -1855,22 +1855,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>伊朗國會初步批准荷姆茲海峽過路費法案 伊朗本幣付錢 | 鉅亨網 - 國際政經</t>
+          <t>白宮：川普有意讓阿拉伯國家為美國打伊朗買單 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-03-31 08:25</t>
+          <t>2026-03-31 08:09</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-31T08:25:34+08:00</t>
+          <t>2026-03-31T08:09:21+08:00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.cnyes.com/news/id/6401957</t>
+          <t>https://news.cnyes.com/news/id/6401960</t>
         </is>
       </c>
     </row>
@@ -1882,74 +1882,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>油價竄升 盟友盼別攻俄油設施 澤倫斯基：俄方停攻能源 烏願對等降級衝突 | 鉅亨網 - 國際政經</t>
+          <t>川普考慮攻占伊朗哈格島 美軍精銳第82空降師數千兵力抵達中東 | 鉅亨網 - 國際政經</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-03-31 08:10</t>
+          <t>2026-03-31 07:34</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-31T08:10:02+08:00</t>
+          <t>2026-03-31T07:34:23+08:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6401920</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>白宮：川普有意讓阿拉伯國家為美國打伊朗買單 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2026-03-31 08:09</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-03-31T08:09:21+08:00</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>https://news.cnyes.com/news/id/6401960</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>鉅亨網</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>川普考慮攻占伊朗哈格島 美軍精銳第82空降師數千兵力抵達中東 | 鉅亨網 - 國際政經</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2026-03-31 07:34</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-03-31T07:34:23+08:00</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
         <is>
           <t>https://news.cnyes.com/news/id/6401944</t>
         </is>
